--- a/diseases/d135/2010-2014.xlsx
+++ b/diseases/d135/2010-2014.xlsx
@@ -3500,28 +3500,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3648,28 +3662,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3796,28 +3824,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3944,28 +3986,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -4092,28 +4148,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4240,28 +4310,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4388,28 +4472,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4536,28 +4634,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4684,28 +4796,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4832,28 +4958,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4980,28 +5120,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5128,28 +5282,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5276,28 +5444,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5424,28 +5606,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5572,28 +5768,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5720,28 +5930,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5868,28 +6092,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6016,28 +6254,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6164,28 +6416,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6312,28 +6578,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6460,28 +6740,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6608,28 +6902,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -6756,28 +7064,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6904,28 +7226,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7052,28 +7388,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7200,28 +7550,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7348,28 +7712,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -7496,28 +7874,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -7644,28 +8036,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7792,28 +8198,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7940,28 +8360,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -8088,28 +8522,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -8236,28 +8684,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8384,28 +8846,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -8532,28 +9008,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -8680,28 +9170,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -8828,28 +9332,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8976,28 +9494,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -9124,28 +9656,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -9272,28 +9818,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -9420,28 +9980,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -9568,28 +10142,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -9716,28 +10304,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9864,28 +10466,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -10012,28 +10628,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -10160,28 +10790,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -10308,28 +10952,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -10456,28 +11114,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -10604,28 +11276,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -10752,28 +11438,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -10900,28 +11600,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -11048,28 +11762,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -11196,28 +11924,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -11344,28 +12086,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -11492,28 +12248,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -11640,28 +12410,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -11788,28 +12572,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -11936,28 +12734,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -12084,28 +12896,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -12232,28 +13058,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -12380,28 +13220,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -12528,28 +13382,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -12676,28 +13544,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -12824,28 +13706,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12972,28 +13868,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -13120,28 +14030,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -13268,28 +14192,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -13416,28 +14354,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -13564,28 +14516,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -13712,28 +14678,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -13860,28 +14840,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -14008,28 +15002,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -14156,28 +15164,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -14304,28 +15326,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -14452,28 +15488,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -14600,28 +15650,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -14748,28 +15812,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -14896,28 +15974,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -15044,28 +16136,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -15192,28 +16298,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -15340,28 +16460,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -15488,28 +16622,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -15636,28 +16784,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -15784,28 +16946,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -15932,28 +17108,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -16080,28 +17270,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -16228,28 +17432,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -16376,28 +17594,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -16524,28 +17756,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -16672,28 +17918,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -16820,28 +18080,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -16968,28 +18242,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -17116,28 +18404,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -17264,28 +18566,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -17412,28 +18728,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -17560,28 +18890,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -17708,28 +19052,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -17856,28 +19214,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -18004,28 +19376,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -18152,28 +19538,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -18300,28 +19700,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -18448,28 +19862,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -18596,28 +20024,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -18744,28 +20186,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -18892,28 +20348,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -19040,28 +20510,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -19188,28 +20672,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -19336,28 +20834,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -19484,28 +20996,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -19632,28 +21158,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -19780,28 +21320,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -19928,28 +21482,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -20076,28 +21644,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -20224,28 +21806,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -20372,28 +21968,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -20520,28 +22130,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -20668,28 +22292,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -20816,28 +22454,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -20964,28 +22616,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -21112,28 +22778,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">

--- a/diseases/d135/2010-2014.xlsx
+++ b/diseases/d135/2010-2014.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,172 +751,107 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2010-01-01</t>
+          <t>2012-09-15</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2010-01</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
+      <c r="R2" t="n">
+        <v>0.004690127753999048</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN2" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -943,17 +878,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -978,172 +913,107 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2010-02-01</t>
+          <t>2012-09-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2010-02</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.007816879589998412</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1040,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1205,172 +1075,107 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2010-03-01</t>
+          <t>2012-09-29</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2010-03</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" t="n">
+        <v>0.003908439794999206</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1202,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1432,172 +1237,107 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2010-04-01</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2010-04</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
+      <c r="R5" t="n">
+        <v>0.004690127753999048</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1364,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1659,172 +1399,107 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2010-05-01</t>
+          <t>2012-10-13</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2010-05</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="R6" t="n">
+        <v>0.006253503671998729</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN6" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1526,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1886,172 +1561,107 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2010-06-01</t>
+          <t>2012-10-20</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2010-06</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="R7" t="n">
+        <v>0.002345063876999524</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2078,17 +1688,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2113,172 +1723,107 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2010-07-01</t>
+          <t>2012-10-27</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2010-07</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="R8" t="n">
+        <v>0.01172531938499762</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN8" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2305,17 +1850,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2340,172 +1885,107 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2010-08-01</t>
+          <t>2012-11-03</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2010-08</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
+      <c r="R9" t="n">
+        <v>0.003126751835999364</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2532,17 +2012,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2567,172 +2047,107 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2010-09-01</t>
+          <t>2012-11-10</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2010-09</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N10" t="n">
+        <v>15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
+      <c r="R10" t="n">
+        <v>0.01172531938499762</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN10" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2759,17 +2174,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2794,172 +2209,107 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2010-10-01</t>
+          <t>2012-11-17</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2010-10</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="R11" t="n">
+        <v>0.002345063876999524</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2986,17 +2336,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3021,172 +2371,107 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2010-11-01</t>
+          <t>2012-11-24</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2010-11</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="R12" t="n">
+        <v>0.005471815712998889</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN12" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3213,17 +2498,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3248,172 +2533,107 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2012-12-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="R13" t="n">
+        <v>0.005471815712998889</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3475,25 +2695,25 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2012-09-15</t>
+          <t>2012-12-08</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.004690127753999048</v>
+        <v>0.006253503671998729</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3637,25 +2857,25 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
+          <t>2012-12-15</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007816879589998412</v>
+        <v>0.004690127753999048</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -3799,25 +3019,25 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2012-09-29</t>
+          <t>2012-12-22</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.003908439794999206</v>
+        <v>0.007816879589998412</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3961,25 +3181,25 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2012-10-06</t>
+          <t>2012-12-29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004690127753999048</v>
+        <v>0.007816879589998412</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -4123,12 +3343,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2012-10-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -4141,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006253503671998729</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -4285,25 +3505,25 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2012-10-20</t>
+          <t>2013-01-12</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.002345063876999524</v>
+        <v>0.003914701917899767</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -4447,25 +3667,25 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2012-10-27</t>
+          <t>2013-01-19</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.01172531938499762</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4609,12 +3829,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2012-11-03</t>
+          <t>2013-01-26</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4627,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.003126751835999364</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4771,25 +3991,25 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2012-11-10</t>
+          <t>2013-02-02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01172531938499762</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4933,25 +4153,25 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2012-11-17</t>
+          <t>2013-02-09</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.002345063876999524</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -5095,25 +4315,25 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2012-11-24</t>
+          <t>2013-02-16</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.005471815712998889</v>
+        <v>0.002348821150739861</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5257,12 +4477,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2013-02-23</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -5275,7 +4495,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.005471815712998889</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5419,25 +4639,25 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2012-12-08</t>
+          <t>2013-03-02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.006253503671998729</v>
+        <v>0.0117441057536993</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5581,25 +4801,25 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2012-12-15</t>
+          <t>2013-03-09</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.004690127753999048</v>
+        <v>0.0117441057536993</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -5743,12 +4963,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2012-12-22</t>
+          <t>2013-03-16</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5761,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.007816879589998412</v>
+        <v>0.007829403835799534</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5905,25 +5125,25 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2012-12-29</t>
+          <t>2013-03-23</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.007816879589998412</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -6067,25 +5287,25 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2013-01-05</t>
+          <t>2013-03-30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6229,25 +5449,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2013-01-12</t>
+          <t>2013-04-06</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.003914701917899767</v>
+        <v>0.007829403835799534</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -6391,25 +5611,25 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2013-01-19</t>
+          <t>2013-04-13</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6553,25 +5773,25 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2013-01-26</t>
+          <t>2013-04-20</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -6715,25 +5935,25 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2013-02-02</t>
+          <t>2013-04-27</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.009395284602959443</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -6877,25 +6097,25 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2013-02-09</t>
+          <t>2013-05-04</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -7039,12 +6259,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2013-02-16</t>
+          <t>2013-05-11</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7201,25 +6421,25 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2013-02-23</t>
+          <t>2013-05-18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -7363,25 +6583,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2013-03-02</t>
+          <t>2013-05-25</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0117441057536993</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7525,25 +6745,25 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2013-03-09</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0117441057536993</v>
+        <v>0.007829403835799534</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -7687,25 +6907,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2013-03-16</t>
+          <t>2013-06-08</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.007829403835799534</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -7849,25 +7069,25 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2013-03-23</t>
+          <t>2013-06-15</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.003914701917899767</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -8011,25 +7231,25 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2013-03-30</t>
+          <t>2013-06-22</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8173,25 +7393,25 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2013-04-06</t>
+          <t>2013-06-29</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.007829403835799534</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -8335,25 +7555,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2013-04-13</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.01017822498653939</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8497,25 +7717,25 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2013-04-20</t>
+          <t>2013-07-13</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -8659,25 +7879,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2013-04-27</t>
+          <t>2013-07-20</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.009395284602959443</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8821,25 +8041,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2013-05-04</t>
+          <t>2013-07-27</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O47" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.01096116537011935</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8983,25 +8203,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2013-08-03</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.002348821150739861</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9145,25 +8365,25 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2013-08-10</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -9307,25 +8527,25 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2013-05-25</t>
+          <t>2013-08-17</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.01017822498653939</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -9469,25 +8689,25 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2013-08-24</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.007829403835799534</v>
+        <v>0.01096116537011935</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9631,25 +8851,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2013-06-08</t>
+          <t>2013-08-31</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -9793,25 +9013,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2013-06-15</t>
+          <t>2013-09-07</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.003914701917899767</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -9955,25 +9175,25 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2013-06-22</t>
+          <t>2013-09-14</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.002348821150739861</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10117,25 +9337,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2013-09-21</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O55" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10279,25 +9499,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2013-09-28</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O56" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01017822498653939</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -10441,25 +9661,25 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2013-07-13</t>
+          <t>2013-10-05</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -10603,25 +9823,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2013-07-20</t>
+          <t>2013-10-12</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.002348821150739861</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10765,25 +9985,25 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2013-07-27</t>
+          <t>2013-10-19</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01096116537011935</v>
+        <v>0.009395284602959443</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -10927,25 +10147,25 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2013-08-03</t>
+          <t>2013-10-26</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11089,25 +10309,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2013-08-10</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -11251,25 +10471,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2013-08-17</t>
+          <t>2013-11-09</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01017822498653939</v>
+        <v>0.0117441057536993</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -11413,25 +10633,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2013-08-24</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O63" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.01096116537011935</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -11575,25 +10795,25 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2013-08-31</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -11737,25 +10957,25 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2013-09-07</t>
+          <t>2013-11-30</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.01017822498653939</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11899,25 +11119,25 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2013-09-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.002348821150739861</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -12061,25 +11281,25 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2013-09-21</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O67" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -12223,25 +11443,25 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2013-09-28</t>
+          <t>2013-12-21</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -12385,25 +11605,25 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2013-10-05</t>
+          <t>2013-12-28</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.003914701917899767</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12547,25 +11767,25 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2013-10-12</t>
+          <t>2014-01-04</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.002348821150739861</v>
+        <v>0.007843961363015201</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -12709,25 +11929,25 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2013-10-19</t>
+          <t>2014-01-11</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O71" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.009395284602959443</v>
+        <v>0.007059565226713681</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -12871,25 +12091,25 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2013-10-26</t>
+          <t>2014-01-18</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -13033,25 +12253,25 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2014-01-25</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O73" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -13195,25 +12415,25 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2013-11-09</t>
+          <t>2014-02-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0117441057536993</v>
+        <v>0.005490772954110641</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -13357,12 +12577,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2013-11-16</t>
+          <t>2014-02-08</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -13375,7 +12595,7 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.007059565226713681</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13519,25 +12739,25 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2014-02-15</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.005490772954110641</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13681,25 +12901,25 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2013-11-30</t>
+          <t>2014-02-22</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O77" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.01017822498653939</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -13843,25 +13063,25 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2013-12-07</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.003921980681507601</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -14005,25 +13225,25 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
+          <t>2014-03-08</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -14167,25 +13387,25 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2013-12-21</t>
+          <t>2014-03-15</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O80" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14329,25 +13549,25 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2013-12-28</t>
+          <t>2014-03-22</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>0.003914701917899767</v>
+        <v>0.003137584545206081</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -14491,25 +13711,25 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2014-01-04</t>
+          <t>2014-03-29</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.007843961363015201</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -14653,25 +13873,25 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2014-01-11</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O83" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.007059565226713681</v>
+        <v>0.01019714977191976</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -14815,12 +14035,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2014-01-18</t>
+          <t>2014-04-12</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -14977,25 +14197,25 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2014-01-25</t>
+          <t>2014-04-19</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O85" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15139,12 +14359,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2014-02-01</t>
+          <t>2014-04-26</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -15301,25 +14521,25 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2014-02-08</t>
+          <t>2014-05-03</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O87" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.007059565226713681</v>
+        <v>0.0117659420445228</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15463,25 +14683,25 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2014-02-15</t>
+          <t>2014-05-10</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.005490772954110641</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -15625,25 +14845,25 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2014-02-22</t>
+          <t>2014-05-17</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.005490772954110641</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -15787,25 +15007,25 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2014-05-24</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.003921980681507601</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -15949,25 +15169,25 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2014-03-08</t>
+          <t>2014-05-31</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.007843961363015201</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -16111,25 +15331,25 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2014-03-15</t>
+          <t>2014-06-07</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O92" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16273,25 +15493,25 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2014-03-22</t>
+          <t>2014-06-14</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.003137584545206081</v>
+        <v>0.003921980681507601</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -16435,25 +15655,25 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2014-03-29</t>
+          <t>2014-06-21</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O94" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.007059565226713681</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -16597,25 +15817,25 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
+          <t>2014-06-28</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O95" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.01019714977191976</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -16759,25 +15979,25 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2014-04-12</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16921,25 +16141,25 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2014-04-19</t>
+          <t>2014-07-12</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O97" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17083,25 +16303,25 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2014-04-26</t>
+          <t>2014-07-19</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O98" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.005490772954110641</v>
+        <v>0.01019714977191976</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -17245,25 +16465,25 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2014-05-03</t>
+          <t>2014-07-26</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O99" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.0117659420445228</v>
+        <v>0.009412753635618243</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17407,25 +16627,25 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2014-05-10</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O100" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.009412753635618243</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17569,12 +16789,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2014-05-17</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -17731,25 +16951,25 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2014-05-24</t>
+          <t>2014-08-16</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O102" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.003137584545206081</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -17893,25 +17113,25 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2014-05-31</t>
+          <t>2014-08-23</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.007843961363015201</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18055,12 +17275,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2014-06-07</t>
+          <t>2014-08-30</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -18217,12 +17437,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2014-06-14</t>
+          <t>2014-09-06</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -18379,25 +17599,25 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2014-06-21</t>
+          <t>2014-09-13</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O106" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.007059565226713681</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -18541,25 +17761,25 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2014-06-28</t>
+          <t>2014-09-20</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O107" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -18703,25 +17923,25 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2014-07-05</t>
+          <t>2014-09-27</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -18865,25 +18085,25 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2014-07-12</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.003137584545206081</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19027,25 +18247,25 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2014-07-19</t>
+          <t>2014-10-11</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O110" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.01019714977191976</v>
+        <v>0.007843961363015201</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19189,12 +18409,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2014-10-18</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N111" t="n">
@@ -19351,25 +18571,25 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O112" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.009412753635618243</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -19513,25 +18733,25 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O113" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>0.005490772954110641</v>
+        <v>0.003137584545206081</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -19675,25 +18895,25 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2014-08-16</t>
+          <t>2014-11-08</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.003137584545206081</v>
+        <v>0.003921980681507601</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -19837,25 +19057,25 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2014-08-23</t>
+          <t>2014-11-15</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.003921980681507601</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -19999,25 +19219,25 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2014-11-22</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.003137584545206081</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -20161,25 +19381,25 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2014-09-06</t>
+          <t>2014-11-29</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O117" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.003921980681507601</v>
+        <v>0.009412753635618243</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20323,25 +19543,25 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2014-09-13</t>
+          <t>2014-12-06</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.007843961363015201</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20485,25 +19705,25 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2014-09-20</t>
+          <t>2014-12-13</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O119" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20647,25 +19867,25 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2014-09-27</t>
+          <t>2014-12-20</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.003921980681507601</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20809,12 +20029,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
+          <t>2014-12-27</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -20908,1950 +20128,6 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>2014-10-11</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>2014-10</t>
-        </is>
-      </c>
-      <c r="N122" t="n">
-        <v>10</v>
-      </c>
-      <c r="O122" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0.007843961363015201</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP122" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV122" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW122" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA122" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB122" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC122" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>2014-10-18</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>2014-10</t>
-        </is>
-      </c>
-      <c r="N123" t="n">
-        <v>12</v>
-      </c>
-      <c r="O123" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.009412753635618243</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP123" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV123" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW123" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA123" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB123" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC123" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>2014-10-25</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>2014-10</t>
-        </is>
-      </c>
-      <c r="N124" t="n">
-        <v>6</v>
-      </c>
-      <c r="O124" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0.004706376817809122</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP124" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV124" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW124" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA124" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB124" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC124" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>2014-11-01</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="N125" t="n">
-        <v>4</v>
-      </c>
-      <c r="O125" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.003137584545206081</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP125" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV125" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA125" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB125" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC125" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>2014-11-08</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="N126" t="n">
-        <v>5</v>
-      </c>
-      <c r="O126" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0.003921980681507601</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV126" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA126" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB126" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC126" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>2014-11-15</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="N127" t="n">
-        <v>5</v>
-      </c>
-      <c r="O127" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.003921980681507601</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV127" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA127" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB127" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC127" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>2014-11-22</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="N128" t="n">
-        <v>4</v>
-      </c>
-      <c r="O128" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0.003137584545206081</v>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP128" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV128" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA128" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB128" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC128" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>2014-11-29</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="N129" t="n">
-        <v>12</v>
-      </c>
-      <c r="O129" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.009412753635618243</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP129" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV129" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW129" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA129" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB129" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC129" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>2014-12-06</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N130" t="n">
-        <v>10</v>
-      </c>
-      <c r="O130" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0.007843961363015201</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP130" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV130" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA130" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB130" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC130" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>2014-12-13</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N131" t="n">
-        <v>11</v>
-      </c>
-      <c r="O131" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0.008628357499316723</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP131" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV131" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW131" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA131" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB131" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC131" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>2014-12-20</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N132" t="n">
-        <v>5</v>
-      </c>
-      <c r="O132" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0.003921980681507601</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV132" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB132" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC132" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>bacterial-meningitis</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>D135</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Bacterial meningitis</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>细菌性脑膜炎</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>2014-12-27</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N133" t="n">
-        <v>4</v>
-      </c>
-      <c r="O133" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.003137584545206081</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV133" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA133" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB133" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC133" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -22902,7 +20178,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2010-01-01</t>
+          <t>2012-09-15</t>
         </is>
       </c>
     </row>
@@ -22983,7 +20259,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -23003,7 +20279,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -23013,7 +20289,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d135/2010-2014.xlsx
+++ b/diseases/d135/2010-2014.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>6</v>
       </c>
+      <c r="P2" t="n">
+        <v>6</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.004690127753999048</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -783,7 +781,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -793,12 +791,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -808,11 +801,6 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -927,17 +915,15 @@
       <c r="O3" t="n">
         <v>10</v>
       </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.007816879589998412</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -945,7 +931,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -955,12 +941,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -970,11 +951,6 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1089,17 +1065,15 @@
       <c r="O4" t="n">
         <v>5</v>
       </c>
+      <c r="P4" t="n">
+        <v>5</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.003908439794999206</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -1107,7 +1081,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1117,12 +1091,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1132,11 +1101,6 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1251,17 +1215,15 @@
       <c r="O5" t="n">
         <v>6</v>
       </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.004690127753999048</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -1269,7 +1231,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1279,12 +1241,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1294,11 +1251,6 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1413,17 +1365,15 @@
       <c r="O6" t="n">
         <v>8</v>
       </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.006253503671998729</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -1431,7 +1381,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1441,12 +1391,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1456,11 +1401,6 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1575,17 +1515,15 @@
       <c r="O7" t="n">
         <v>3</v>
       </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.002345063876999524</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -1593,7 +1531,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1603,12 +1541,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1618,11 +1551,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1737,17 +1665,15 @@
       <c r="O8" t="n">
         <v>15</v>
       </c>
+      <c r="P8" t="n">
+        <v>15</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.01172531938499762</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -1755,7 +1681,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1765,12 +1691,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1780,11 +1701,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1899,17 +1815,15 @@
       <c r="O9" t="n">
         <v>4</v>
       </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.003126751835999364</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -1917,7 +1831,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1927,12 +1841,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1942,11 +1851,6 @@
       </c>
       <c r="AT9" t="n">
         <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2061,17 +1965,15 @@
       <c r="O10" t="n">
         <v>15</v>
       </c>
+      <c r="P10" t="n">
+        <v>15</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.01172531938499762</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -2079,7 +1981,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2089,12 +1991,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2104,11 +2001,6 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2223,17 +2115,15 @@
       <c r="O11" t="n">
         <v>3</v>
       </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.002345063876999524</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -2241,7 +2131,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2251,12 +2141,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2266,11 +2151,6 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2385,17 +2265,15 @@
       <c r="O12" t="n">
         <v>7</v>
       </c>
+      <c r="P12" t="n">
+        <v>7</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.005471815712998889</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -2403,7 +2281,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2413,12 +2291,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2428,11 +2301,6 @@
       </c>
       <c r="AT12" t="n">
         <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2547,17 +2415,15 @@
       <c r="O13" t="n">
         <v>7</v>
       </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.005471815712998889</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -2565,7 +2431,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2575,12 +2441,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2590,11 +2451,6 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2709,17 +2565,15 @@
       <c r="O14" t="n">
         <v>8</v>
       </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.006253503671998729</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -2727,7 +2581,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2737,12 +2591,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2752,11 +2601,6 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2871,17 +2715,15 @@
       <c r="O15" t="n">
         <v>6</v>
       </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.004690127753999048</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -2889,7 +2731,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2899,12 +2741,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2914,11 +2751,6 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3033,17 +2865,15 @@
       <c r="O16" t="n">
         <v>10</v>
       </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.007816879589998412</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -3051,7 +2881,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3061,12 +2891,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3076,11 +2901,6 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3195,17 +3015,15 @@
       <c r="O17" t="n">
         <v>10</v>
       </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.007816879589998412</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -3213,7 +3031,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3223,12 +3041,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3238,11 +3051,6 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3357,17 +3165,15 @@
       <c r="O18" t="n">
         <v>8</v>
       </c>
+      <c r="P18" t="n">
+        <v>8</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -3375,7 +3181,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3385,12 +3191,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3400,11 +3201,6 @@
       </c>
       <c r="AT18" t="n">
         <v>1</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3519,17 +3315,15 @@
       <c r="O19" t="n">
         <v>5</v>
       </c>
+      <c r="P19" t="n">
+        <v>5</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.003914701917899767</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -3537,7 +3331,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3547,12 +3341,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3562,11 +3351,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3681,17 +3465,15 @@
       <c r="O20" t="n">
         <v>6</v>
       </c>
+      <c r="P20" t="n">
+        <v>6</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -3699,7 +3481,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3709,12 +3491,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3724,11 +3501,6 @@
       </c>
       <c r="AT20" t="n">
         <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3843,17 +3615,15 @@
       <c r="O21" t="n">
         <v>4</v>
       </c>
+      <c r="P21" t="n">
+        <v>4</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -3861,7 +3631,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3871,12 +3641,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -3886,11 +3651,6 @@
       </c>
       <c r="AT21" t="n">
         <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4005,17 +3765,15 @@
       <c r="O22" t="n">
         <v>7</v>
       </c>
+      <c r="P22" t="n">
+        <v>7</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -4023,7 +3781,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -4033,12 +3791,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4048,11 +3801,6 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4167,17 +3915,15 @@
       <c r="O23" t="n">
         <v>11</v>
       </c>
+      <c r="P23" t="n">
+        <v>11</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.008612344219379489</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -4185,7 +3931,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4195,12 +3941,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4210,11 +3951,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4329,17 +4065,15 @@
       <c r="O24" t="n">
         <v>3</v>
       </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -4347,7 +4081,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4357,12 +4091,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4372,11 +4101,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4491,17 +4215,15 @@
       <c r="O25" t="n">
         <v>7</v>
       </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -4509,7 +4231,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4519,12 +4241,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4534,11 +4251,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4653,17 +4365,15 @@
       <c r="O26" t="n">
         <v>15</v>
       </c>
+      <c r="P26" t="n">
+        <v>15</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0.0117441057536993</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -4671,7 +4381,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4681,12 +4391,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4696,11 +4401,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4815,17 +4515,15 @@
       <c r="O27" t="n">
         <v>15</v>
       </c>
+      <c r="P27" t="n">
+        <v>15</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0.0117441057536993</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -4833,7 +4531,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4843,12 +4541,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4858,11 +4551,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4977,17 +4665,15 @@
       <c r="O28" t="n">
         <v>10</v>
       </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0.007829403835799534</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -4995,7 +4681,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5005,12 +4691,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -5020,11 +4701,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5139,17 +4815,15 @@
       <c r="O29" t="n">
         <v>6</v>
       </c>
+      <c r="P29" t="n">
+        <v>6</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -5157,7 +4831,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -5167,12 +4841,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5182,11 +4851,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5301,17 +4965,15 @@
       <c r="O30" t="n">
         <v>9</v>
       </c>
+      <c r="P30" t="n">
+        <v>9</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0.007046463452219581</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -5319,7 +4981,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5329,12 +4991,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -5344,11 +5001,6 @@
       </c>
       <c r="AT30" t="n">
         <v>1</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5463,17 +5115,15 @@
       <c r="O31" t="n">
         <v>10</v>
       </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0.007829403835799534</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -5481,7 +5131,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5491,12 +5141,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -5506,11 +5151,6 @@
       </c>
       <c r="AT31" t="n">
         <v>1</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5625,17 +5265,15 @@
       <c r="O32" t="n">
         <v>9</v>
       </c>
+      <c r="P32" t="n">
+        <v>9</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0.007046463452219581</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -5643,7 +5281,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5653,12 +5291,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5668,11 +5301,6 @@
       </c>
       <c r="AT32" t="n">
         <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5787,17 +5415,15 @@
       <c r="O33" t="n">
         <v>11</v>
       </c>
+      <c r="P33" t="n">
+        <v>11</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0.008612344219379489</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -5805,7 +5431,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5815,12 +5441,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -5830,11 +5451,6 @@
       </c>
       <c r="AT33" t="n">
         <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5949,17 +5565,15 @@
       <c r="O34" t="n">
         <v>12</v>
       </c>
+      <c r="P34" t="n">
+        <v>12</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0.009395284602959443</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -5967,7 +5581,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5977,12 +5591,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -5992,11 +5601,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6111,17 +5715,15 @@
       <c r="O35" t="n">
         <v>9</v>
       </c>
+      <c r="P35" t="n">
+        <v>9</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0.007046463452219581</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -6129,7 +5731,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -6139,12 +5741,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -6154,11 +5751,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6273,17 +5865,15 @@
       <c r="O36" t="n">
         <v>3</v>
       </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -6291,7 +5881,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -6301,12 +5891,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -6316,11 +5901,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6435,17 +6015,15 @@
       <c r="O37" t="n">
         <v>9</v>
       </c>
+      <c r="P37" t="n">
+        <v>9</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0.007046463452219581</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -6453,7 +6031,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6463,12 +6041,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6478,11 +6051,6 @@
       </c>
       <c r="AT37" t="n">
         <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6597,17 +6165,15 @@
       <c r="O38" t="n">
         <v>8</v>
       </c>
+      <c r="P38" t="n">
+        <v>8</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -6615,7 +6181,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6625,12 +6191,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -6640,11 +6201,6 @@
       </c>
       <c r="AT38" t="n">
         <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6759,17 +6315,15 @@
       <c r="O39" t="n">
         <v>10</v>
       </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0.007829403835799534</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -6777,7 +6331,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6787,12 +6341,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6802,11 +6351,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6921,17 +6465,15 @@
       <c r="O40" t="n">
         <v>7</v>
       </c>
+      <c r="P40" t="n">
+        <v>7</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -6939,7 +6481,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6949,12 +6491,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6964,11 +6501,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7083,17 +6615,15 @@
       <c r="O41" t="n">
         <v>5</v>
       </c>
+      <c r="P41" t="n">
+        <v>5</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0.003914701917899767</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -7101,7 +6631,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -7111,12 +6641,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -7126,11 +6651,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7245,17 +6765,15 @@
       <c r="O42" t="n">
         <v>7</v>
       </c>
+      <c r="P42" t="n">
+        <v>7</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -7263,7 +6781,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -7273,12 +6791,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -7288,11 +6801,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7407,17 +6915,15 @@
       <c r="O43" t="n">
         <v>11</v>
       </c>
+      <c r="P43" t="n">
+        <v>11</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0.008612344219379489</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -7425,7 +6931,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7435,12 +6941,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7450,11 +6951,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7569,17 +7065,15 @@
       <c r="O44" t="n">
         <v>13</v>
       </c>
+      <c r="P44" t="n">
+        <v>13</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0.01017822498653939</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -7587,7 +7081,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7597,12 +7091,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -7612,11 +7101,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7731,17 +7215,15 @@
       <c r="O45" t="n">
         <v>4</v>
       </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -7749,7 +7231,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7759,12 +7241,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7774,11 +7251,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7893,17 +7365,15 @@
       <c r="O46" t="n">
         <v>7</v>
       </c>
+      <c r="P46" t="n">
+        <v>7</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -7911,7 +7381,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7921,12 +7391,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -7936,11 +7401,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8055,17 +7515,15 @@
       <c r="O47" t="n">
         <v>14</v>
       </c>
+      <c r="P47" t="n">
+        <v>14</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0.01096116537011935</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -8073,7 +7531,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -8083,12 +7541,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -8098,11 +7551,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8217,17 +7665,15 @@
       <c r="O48" t="n">
         <v>8</v>
       </c>
+      <c r="P48" t="n">
+        <v>8</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -8235,7 +7681,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8245,12 +7691,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -8260,11 +7701,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8379,17 +7815,15 @@
       <c r="O49" t="n">
         <v>8</v>
       </c>
+      <c r="P49" t="n">
+        <v>8</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -8397,7 +7831,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8407,12 +7841,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -8422,11 +7851,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8541,17 +7965,15 @@
       <c r="O50" t="n">
         <v>13</v>
       </c>
+      <c r="P50" t="n">
+        <v>13</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0.01017822498653939</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -8559,7 +7981,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8569,12 +7991,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -8584,11 +8001,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8703,17 +8115,15 @@
       <c r="O51" t="n">
         <v>14</v>
       </c>
+      <c r="P51" t="n">
+        <v>14</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0.01096116537011935</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -8721,7 +8131,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8731,12 +8141,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8746,11 +8151,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8865,17 +8265,15 @@
       <c r="O52" t="n">
         <v>6</v>
       </c>
+      <c r="P52" t="n">
+        <v>6</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -8883,7 +8281,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8893,12 +8291,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -8908,11 +8301,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -9027,17 +8415,15 @@
       <c r="O53" t="n">
         <v>6</v>
       </c>
+      <c r="P53" t="n">
+        <v>6</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -9045,7 +8431,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -9055,12 +8441,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -9070,11 +8451,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9189,17 +8565,15 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
+      <c r="P54" t="n">
+        <v>3</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -9207,7 +8581,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9217,12 +8591,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -9232,11 +8601,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9351,17 +8715,15 @@
       <c r="O55" t="n">
         <v>4</v>
       </c>
+      <c r="P55" t="n">
+        <v>4</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -9369,7 +8731,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9379,12 +8741,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -9394,11 +8751,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9513,17 +8865,15 @@
       <c r="O56" t="n">
         <v>9</v>
       </c>
+      <c r="P56" t="n">
+        <v>9</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0.007046463452219581</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -9531,7 +8881,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9541,12 +8891,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -9556,11 +8901,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9675,17 +9015,15 @@
       <c r="O57" t="n">
         <v>8</v>
       </c>
+      <c r="P57" t="n">
+        <v>8</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -9693,7 +9031,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9703,12 +9041,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -9718,11 +9051,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9837,17 +9165,15 @@
       <c r="O58" t="n">
         <v>3</v>
       </c>
+      <c r="P58" t="n">
+        <v>3</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -9855,7 +9181,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9865,12 +9191,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -9880,11 +9201,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9999,17 +9315,15 @@
       <c r="O59" t="n">
         <v>12</v>
       </c>
+      <c r="P59" t="n">
+        <v>12</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0.009395284602959443</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -10017,7 +9331,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -10027,12 +9341,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -10042,11 +9351,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -10161,17 +9465,15 @@
       <c r="O60" t="n">
         <v>4</v>
       </c>
+      <c r="P60" t="n">
+        <v>4</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -10179,7 +9481,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -10189,12 +9491,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -10204,11 +9501,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -10323,17 +9615,15 @@
       <c r="O61" t="n">
         <v>11</v>
       </c>
+      <c r="P61" t="n">
+        <v>11</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0.008612344219379489</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -10341,7 +9631,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10351,12 +9641,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -10366,11 +9651,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10485,17 +9765,15 @@
       <c r="O62" t="n">
         <v>15</v>
       </c>
+      <c r="P62" t="n">
+        <v>15</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0.0117441057536993</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -10503,7 +9781,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10513,12 +9791,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -10528,11 +9801,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10647,17 +9915,15 @@
       <c r="O63" t="n">
         <v>9</v>
       </c>
+      <c r="P63" t="n">
+        <v>9</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0.007046463452219581</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -10665,7 +9931,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -10675,12 +9941,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -10690,11 +9951,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10809,17 +10065,15 @@
       <c r="O64" t="n">
         <v>8</v>
       </c>
+      <c r="P64" t="n">
+        <v>8</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -10827,7 +10081,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10837,12 +10091,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -10852,11 +10101,6 @@
       </c>
       <c r="AT64" t="n">
         <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10971,17 +10215,15 @@
       <c r="O65" t="n">
         <v>13</v>
       </c>
+      <c r="P65" t="n">
+        <v>13</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0.01017822498653939</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -10989,7 +10231,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10999,12 +10241,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -11014,11 +10251,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11133,17 +10365,15 @@
       <c r="O66" t="n">
         <v>4</v>
       </c>
+      <c r="P66" t="n">
+        <v>4</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -11151,7 +10381,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -11161,12 +10391,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -11176,11 +10401,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -11295,17 +10515,15 @@
       <c r="O67" t="n">
         <v>11</v>
       </c>
+      <c r="P67" t="n">
+        <v>11</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0.008612344219379489</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -11313,7 +10531,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -11323,12 +10541,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -11338,11 +10551,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11457,17 +10665,15 @@
       <c r="O68" t="n">
         <v>7</v>
       </c>
+      <c r="P68" t="n">
+        <v>7</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -11475,7 +10681,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11485,12 +10691,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -11500,11 +10701,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11619,17 +10815,15 @@
       <c r="O69" t="n">
         <v>5</v>
       </c>
+      <c r="P69" t="n">
+        <v>5</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0.003914701917899767</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -11637,7 +10831,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11647,12 +10841,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -11662,11 +10851,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11781,17 +10965,15 @@
       <c r="O70" t="n">
         <v>10</v>
       </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0.007843961363015201</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -11799,7 +10981,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11809,12 +10991,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -11824,11 +11001,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11943,17 +11115,15 @@
       <c r="O71" t="n">
         <v>9</v>
       </c>
+      <c r="P71" t="n">
+        <v>9</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0.007059565226713681</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -11961,7 +11131,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11971,12 +11141,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -11986,11 +11151,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -12105,17 +11265,15 @@
       <c r="O72" t="n">
         <v>6</v>
       </c>
+      <c r="P72" t="n">
+        <v>6</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -12123,7 +11281,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -12133,12 +11291,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -12148,11 +11301,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -12267,17 +11415,15 @@
       <c r="O73" t="n">
         <v>6</v>
       </c>
+      <c r="P73" t="n">
+        <v>6</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -12285,7 +11431,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12295,12 +11441,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -12310,11 +11451,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -12429,17 +11565,15 @@
       <c r="O74" t="n">
         <v>7</v>
       </c>
+      <c r="P74" t="n">
+        <v>7</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -12447,7 +11581,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12457,12 +11591,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -12472,11 +11601,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12591,17 +11715,15 @@
       <c r="O75" t="n">
         <v>9</v>
       </c>
+      <c r="P75" t="n">
+        <v>9</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0.007059565226713681</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -12609,7 +11731,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12619,12 +11741,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -12634,11 +11751,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12753,17 +11865,15 @@
       <c r="O76" t="n">
         <v>7</v>
       </c>
+      <c r="P76" t="n">
+        <v>7</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -12771,7 +11881,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12781,12 +11891,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -12796,11 +11901,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12915,17 +12015,15 @@
       <c r="O77" t="n">
         <v>3</v>
       </c>
+      <c r="P77" t="n">
+        <v>3</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -12933,7 +12031,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12943,12 +12041,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -12958,11 +12051,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -13077,17 +12165,15 @@
       <c r="O78" t="n">
         <v>5</v>
       </c>
+      <c r="P78" t="n">
+        <v>5</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -13095,7 +12181,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -13105,12 +12191,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -13120,11 +12201,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -13239,17 +12315,15 @@
       <c r="O79" t="n">
         <v>8</v>
       </c>
+      <c r="P79" t="n">
+        <v>8</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0.006275169090412163</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -13257,7 +12331,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13267,12 +12341,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -13282,11 +12351,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -13401,17 +12465,15 @@
       <c r="O80" t="n">
         <v>11</v>
       </c>
+      <c r="P80" t="n">
+        <v>11</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0.008628357499316723</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -13419,7 +12481,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13429,12 +12491,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -13444,11 +12501,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -13563,17 +12615,15 @@
       <c r="O81" t="n">
         <v>4</v>
       </c>
+      <c r="P81" t="n">
+        <v>4</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -13581,7 +12631,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13591,12 +12641,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -13606,11 +12651,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13725,17 +12765,15 @@
       <c r="O82" t="n">
         <v>11</v>
       </c>
+      <c r="P82" t="n">
+        <v>11</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0.008628357499316723</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -13743,7 +12781,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13753,12 +12791,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -13768,11 +12801,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13887,17 +12915,15 @@
       <c r="O83" t="n">
         <v>13</v>
       </c>
+      <c r="P83" t="n">
+        <v>13</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0.01019714977191976</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -13905,7 +12931,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13915,12 +12941,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -13930,11 +12951,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -14049,17 +13065,15 @@
       <c r="O84" t="n">
         <v>6</v>
       </c>
+      <c r="P84" t="n">
+        <v>6</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -14067,7 +13081,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -14077,12 +13091,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -14092,11 +13101,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -14211,17 +13215,15 @@
       <c r="O85" t="n">
         <v>11</v>
       </c>
+      <c r="P85" t="n">
+        <v>11</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0.008628357499316723</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -14229,7 +13231,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -14239,12 +13241,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -14254,11 +13251,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14373,17 +13365,15 @@
       <c r="O86" t="n">
         <v>7</v>
       </c>
+      <c r="P86" t="n">
+        <v>7</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -14391,7 +13381,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14401,12 +13391,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -14416,11 +13401,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -14535,17 +13515,15 @@
       <c r="O87" t="n">
         <v>15</v>
       </c>
+      <c r="P87" t="n">
+        <v>15</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0.0117659420445228</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -14553,7 +13531,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14563,12 +13541,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -14578,11 +13551,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -14697,17 +13665,15 @@
       <c r="O88" t="n">
         <v>3</v>
       </c>
+      <c r="P88" t="n">
+        <v>3</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -14715,7 +13681,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14725,12 +13691,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -14740,11 +13701,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14859,17 +13815,15 @@
       <c r="O89" t="n">
         <v>7</v>
       </c>
+      <c r="P89" t="n">
+        <v>7</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -14877,7 +13831,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14887,12 +13841,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -14902,11 +13851,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -15021,17 +13965,15 @@
       <c r="O90" t="n">
         <v>8</v>
       </c>
+      <c r="P90" t="n">
+        <v>8</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0.006275169090412163</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -15039,7 +13981,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -15049,12 +13991,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -15064,11 +14001,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -15183,17 +14115,15 @@
       <c r="O91" t="n">
         <v>10</v>
       </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0.007843961363015201</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -15201,7 +14131,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -15211,12 +14141,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -15226,11 +14151,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15345,17 +14265,15 @@
       <c r="O92" t="n">
         <v>6</v>
       </c>
+      <c r="P92" t="n">
+        <v>6</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -15363,7 +14281,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -15373,12 +14291,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -15388,11 +14301,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -15507,17 +14415,15 @@
       <c r="O93" t="n">
         <v>5</v>
       </c>
+      <c r="P93" t="n">
+        <v>5</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -15525,7 +14431,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15535,12 +14441,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -15550,11 +14451,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -15669,17 +14565,15 @@
       <c r="O94" t="n">
         <v>9</v>
       </c>
+      <c r="P94" t="n">
+        <v>9</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0.007059565226713681</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -15687,7 +14581,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15697,12 +14591,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -15712,11 +14601,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -15831,17 +14715,15 @@
       <c r="O95" t="n">
         <v>8</v>
       </c>
+      <c r="P95" t="n">
+        <v>8</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0.006275169090412163</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -15849,7 +14731,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15859,12 +14741,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -15874,11 +14751,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15993,17 +14865,15 @@
       <c r="O96" t="n">
         <v>8</v>
       </c>
+      <c r="P96" t="n">
+        <v>8</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0.006275169090412163</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -16011,7 +14881,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -16021,12 +14891,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -16036,11 +14901,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -16155,17 +15015,15 @@
       <c r="O97" t="n">
         <v>6</v>
       </c>
+      <c r="P97" t="n">
+        <v>6</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -16173,7 +15031,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -16183,12 +15041,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -16198,11 +15051,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -16317,17 +15165,15 @@
       <c r="O98" t="n">
         <v>13</v>
       </c>
+      <c r="P98" t="n">
+        <v>13</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0.01019714977191976</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -16335,7 +15181,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -16345,12 +15191,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -16360,11 +15201,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -16479,17 +15315,15 @@
       <c r="O99" t="n">
         <v>12</v>
       </c>
+      <c r="P99" t="n">
+        <v>12</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0.009412753635618243</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -16497,7 +15331,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -16507,12 +15341,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -16522,11 +15351,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -16641,17 +15465,15 @@
       <c r="O100" t="n">
         <v>12</v>
       </c>
+      <c r="P100" t="n">
+        <v>12</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0.009412753635618243</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -16659,7 +15481,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -16669,12 +15491,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -16684,11 +15501,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -16803,17 +15615,15 @@
       <c r="O101" t="n">
         <v>7</v>
       </c>
+      <c r="P101" t="n">
+        <v>7</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -16821,7 +15631,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16831,12 +15641,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -16846,11 +15651,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -16965,17 +15765,15 @@
       <c r="O102" t="n">
         <v>4</v>
       </c>
+      <c r="P102" t="n">
+        <v>4</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -16983,7 +15781,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16993,12 +15791,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -17008,11 +15801,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -17127,17 +15915,15 @@
       <c r="O103" t="n">
         <v>11</v>
       </c>
+      <c r="P103" t="n">
+        <v>11</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0.008628357499316723</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -17145,7 +15931,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -17155,12 +15941,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -17170,11 +15951,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -17289,17 +16065,15 @@
       <c r="O104" t="n">
         <v>6</v>
       </c>
+      <c r="P104" t="n">
+        <v>6</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -17307,7 +16081,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -17317,12 +16091,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -17332,11 +16101,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -17451,17 +16215,15 @@
       <c r="O105" t="n">
         <v>5</v>
       </c>
+      <c r="P105" t="n">
+        <v>5</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -17469,7 +16231,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -17479,12 +16241,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -17494,11 +16251,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -17613,17 +16365,15 @@
       <c r="O106" t="n">
         <v>6</v>
       </c>
+      <c r="P106" t="n">
+        <v>6</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -17631,7 +16381,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -17641,12 +16391,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -17656,11 +16401,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -17775,17 +16515,15 @@
       <c r="O107" t="n">
         <v>3</v>
       </c>
+      <c r="P107" t="n">
+        <v>3</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -17793,7 +16531,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -17803,12 +16541,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -17818,11 +16551,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -17937,17 +16665,15 @@
       <c r="O108" t="n">
         <v>3</v>
       </c>
+      <c r="P108" t="n">
+        <v>3</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -17955,7 +16681,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17965,12 +16691,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -17980,11 +16701,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -18099,17 +16815,15 @@
       <c r="O109" t="n">
         <v>4</v>
       </c>
+      <c r="P109" t="n">
+        <v>4</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -18117,7 +16831,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -18127,12 +16841,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -18142,11 +16851,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -18261,17 +16965,15 @@
       <c r="O110" t="n">
         <v>10</v>
       </c>
+      <c r="P110" t="n">
+        <v>10</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0.007843961363015201</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -18279,7 +16981,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -18289,12 +16991,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -18304,11 +17001,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -18423,17 +17115,15 @@
       <c r="O111" t="n">
         <v>12</v>
       </c>
+      <c r="P111" t="n">
+        <v>12</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0.009412753635618243</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -18441,7 +17131,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -18451,12 +17141,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -18466,11 +17151,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -18585,17 +17265,15 @@
       <c r="O112" t="n">
         <v>6</v>
       </c>
+      <c r="P112" t="n">
+        <v>6</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -18603,7 +17281,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -18613,12 +17291,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -18628,11 +17301,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -18747,17 +17415,15 @@
       <c r="O113" t="n">
         <v>4</v>
       </c>
+      <c r="P113" t="n">
+        <v>4</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -18765,7 +17431,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -18775,12 +17441,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -18790,11 +17451,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -18909,17 +17565,15 @@
       <c r="O114" t="n">
         <v>5</v>
       </c>
+      <c r="P114" t="n">
+        <v>5</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -18927,7 +17581,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18937,12 +17591,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -18952,11 +17601,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -19071,17 +17715,15 @@
       <c r="O115" t="n">
         <v>5</v>
       </c>
+      <c r="P115" t="n">
+        <v>5</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -19089,7 +17731,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -19099,12 +17741,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -19114,11 +17751,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -19233,17 +17865,15 @@
       <c r="O116" t="n">
         <v>4</v>
       </c>
+      <c r="P116" t="n">
+        <v>4</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -19251,7 +17881,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -19261,12 +17891,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -19276,11 +17901,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -19395,17 +18015,15 @@
       <c r="O117" t="n">
         <v>12</v>
       </c>
+      <c r="P117" t="n">
+        <v>12</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0.009412753635618243</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -19413,7 +18031,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -19423,12 +18041,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -19438,11 +18051,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -19557,17 +18165,15 @@
       <c r="O118" t="n">
         <v>10</v>
       </c>
+      <c r="P118" t="n">
+        <v>10</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0.007843961363015201</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -19575,7 +18181,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -19585,12 +18191,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -19600,11 +18201,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -19719,17 +18315,15 @@
       <c r="O119" t="n">
         <v>11</v>
       </c>
+      <c r="P119" t="n">
+        <v>11</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0.008628357499316723</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -19737,7 +18331,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -19747,12 +18341,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -19762,11 +18351,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -19881,17 +18465,15 @@
       <c r="O120" t="n">
         <v>5</v>
       </c>
+      <c r="P120" t="n">
+        <v>5</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -19899,7 +18481,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -19909,12 +18491,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -19924,11 +18501,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -20043,17 +18615,15 @@
       <c r="O121" t="n">
         <v>4</v>
       </c>
+      <c r="P121" t="n">
+        <v>4</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
@@ -20061,7 +18631,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -20071,12 +18641,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -20086,11 +18651,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>

--- a/diseases/d135/2010-2014.xlsx
+++ b/diseases/d135/2010-2014.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,95 +751,172 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2012-09-15</t>
+          <t>2010-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>0.004690127753999048</v>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -866,17 +943,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -901,95 +978,172 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
+          <t>2010-02-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2010-02</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O3" t="n">
-        <v>10</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0.007816879589998412</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1016,17 +1170,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1051,95 +1205,172 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2012-09-29</t>
+          <t>2010-03-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2010-03</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>0.003908439794999206</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>0</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1166,17 +1397,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1201,95 +1432,172 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2012-10-06</t>
+          <t>2010-04-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-04</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.004690127753999048</v>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>0</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1624,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1351,95 +1659,172 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2012-10-13</t>
+          <t>2010-05-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-05</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>8</v>
-      </c>
-      <c r="P6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.006253503671998729</v>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>0</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1466,17 +1851,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1501,95 +1886,172 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2012-10-20</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-06</t>
         </is>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.002345063876999524</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1616,17 +2078,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1651,95 +2113,172 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2012-10-27</t>
+          <t>2010-07-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-07</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
-      </c>
-      <c r="O8" t="n">
-        <v>15</v>
-      </c>
-      <c r="P8" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.01172531938499762</v>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>0</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1766,17 +2305,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1801,95 +2340,172 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2012-11-03</t>
+          <t>2010-08-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-08</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>0.003126751835999364</v>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1916,17 +2532,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1951,95 +2567,172 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2012-11-10</t>
+          <t>2010-09-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-09</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>15</v>
-      </c>
-      <c r="O10" t="n">
-        <v>15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>0.01172531938499762</v>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>0</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2759,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2101,95 +2794,172 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2012-11-17</t>
+          <t>2010-10-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-10</t>
         </is>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
         <v>3</v>
       </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.002345063876999524</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>1</v>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2216,17 +2986,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2251,95 +3021,172 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2012-11-24</t>
+          <t>2010-11-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-11</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.005471815712998889</v>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>0</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2366,17 +3213,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2401,95 +3248,172 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2010-12-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>0.005471815712998889</v>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>0</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2551,28 +3475,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2012-12-08</t>
+          <t>2012-09-15</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.006253503671998729</v>
+        <v>0.004690127753999048</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2701,28 +3625,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2012-12-15</t>
+          <t>2012-09-22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.004690127753999048</v>
+        <v>0.007816879589998412</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2851,28 +3775,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2012-12-22</t>
+          <t>2012-09-29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.007816879589998412</v>
+        <v>0.003908439794999206</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3001,28 +3925,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2012-12-29</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.007816879589998412</v>
+        <v>0.004690127753999048</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3151,12 +4075,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2013-01-05</t>
+          <t>2012-10-13</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3172,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.006253503671998729</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3301,28 +4225,28 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2013-01-12</t>
+          <t>2012-10-20</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.003914701917899767</v>
+        <v>0.002345063876999524</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -3451,28 +4375,28 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2013-01-19</t>
+          <t>2012-10-27</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.01172531938499762</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3601,12 +4525,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2013-01-26</t>
+          <t>2012-11-03</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3622,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.003126751835999364</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3751,28 +4675,28 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2013-02-02</t>
+          <t>2012-11-10</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P22" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.01172531938499762</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3901,28 +4825,28 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2013-02-09</t>
+          <t>2012-11-17</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.002345063876999524</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -4051,28 +4975,28 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2013-02-16</t>
+          <t>2012-11-24</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.002348821150739861</v>
+        <v>0.005471815712998889</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -4201,12 +5125,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2013-02-23</t>
+          <t>2012-12-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4222,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.005471815712998889</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4351,28 +5275,28 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2013-03-02</t>
+          <t>2012-12-08</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0117441057536993</v>
+        <v>0.006253503671998729</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -4501,28 +5425,28 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2013-03-09</t>
+          <t>2012-12-15</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0117441057536993</v>
+        <v>0.004690127753999048</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4651,12 +5575,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2013-03-16</t>
+          <t>2012-12-22</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4672,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.007829403835799534</v>
+        <v>0.007816879589998412</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4801,28 +5725,28 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2013-03-23</t>
+          <t>2012-12-29</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.007816879589998412</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4951,28 +5875,28 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2013-03-30</t>
+          <t>2013-01-05</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5101,28 +6025,28 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2013-04-06</t>
+          <t>2013-01-12</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007829403835799534</v>
+        <v>0.003914701917899767</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -5251,28 +6175,28 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2013-04-13</t>
+          <t>2013-01-19</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -5401,28 +6325,28 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2013-04-20</t>
+          <t>2013-01-26</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -5551,28 +6475,28 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2013-04-27</t>
+          <t>2013-02-02</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.009395284602959443</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5701,28 +6625,28 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2013-05-04</t>
+          <t>2013-02-09</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5851,12 +6775,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2013-02-16</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6001,28 +6925,28 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2013-02-23</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -6151,28 +7075,28 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2013-05-25</t>
+          <t>2013-03-02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.0117441057536993</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6301,28 +7225,28 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2013-03-09</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.007829403835799534</v>
+        <v>0.0117441057536993</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6451,28 +7375,28 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2013-06-08</t>
+          <t>2013-03-16</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.007829403835799534</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6601,28 +7525,28 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2013-06-15</t>
+          <t>2013-03-23</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.003914701917899767</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6751,28 +7675,28 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2013-06-22</t>
+          <t>2013-03-30</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6901,28 +7825,28 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2013-04-06</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.007829403835799534</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -7051,28 +7975,28 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2013-04-13</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01017822498653939</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -7201,28 +8125,28 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2013-07-13</t>
+          <t>2013-04-20</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7351,28 +8275,28 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2013-07-20</t>
+          <t>2013-04-27</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.009395284602959443</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7501,28 +8425,28 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2013-07-27</t>
+          <t>2013-05-04</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O47" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P47" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01096116537011935</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7651,28 +8575,28 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2013-08-03</t>
+          <t>2013-05-11</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.002348821150739861</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7801,28 +8725,28 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2013-08-10</t>
+          <t>2013-05-18</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7951,28 +8875,28 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2013-08-17</t>
+          <t>2013-05-25</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01017822498653939</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -8101,28 +9025,28 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2013-08-24</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O51" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P51" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01096116537011935</v>
+        <v>0.007829403835799534</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -8251,28 +9175,28 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2013-08-31</t>
+          <t>2013-06-08</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8401,28 +9325,28 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2013-09-07</t>
+          <t>2013-06-15</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004697642301479722</v>
+        <v>0.003914701917899767</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -8551,28 +9475,28 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2013-09-14</t>
+          <t>2013-06-22</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.002348821150739861</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8701,28 +9625,28 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2013-09-21</t>
+          <t>2013-06-29</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P55" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8851,28 +9775,28 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2013-09-28</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O56" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P56" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.01017822498653939</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9001,28 +9925,28 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2013-10-05</t>
+          <t>2013-07-13</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9151,28 +10075,28 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2013-10-12</t>
+          <t>2013-07-20</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.002348821150739861</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -9301,28 +10225,28 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2013-10-19</t>
+          <t>2013-07-27</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.009395284602959443</v>
+        <v>0.01096116537011935</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -9451,28 +10375,28 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2013-10-26</t>
+          <t>2013-08-03</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -9601,28 +10525,28 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2013-08-10</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -9751,28 +10675,28 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2013-11-09</t>
+          <t>2013-08-17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0117441057536993</v>
+        <v>0.01017822498653939</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -9901,28 +10825,28 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2013-11-16</t>
+          <t>2013-08-24</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O63" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P63" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007046463452219581</v>
+        <v>0.01096116537011935</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -10051,28 +10975,28 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2013-08-31</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.006263523068639628</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -10201,28 +11125,28 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2013-11-30</t>
+          <t>2013-09-07</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O65" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P65" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01017822498653939</v>
+        <v>0.004697642301479722</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -10351,28 +11275,28 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2013-12-07</t>
+          <t>2013-09-14</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.003131761534319814</v>
+        <v>0.002348821150739861</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -10501,28 +11425,28 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
+          <t>2013-09-21</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O67" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.008612344219379489</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10651,28 +11575,28 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2013-12-21</t>
+          <t>2013-09-28</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.005480582685059674</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10801,28 +11725,28 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2013-12-28</t>
+          <t>2013-10-05</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.003914701917899767</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -10951,28 +11875,28 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2014-01-04</t>
+          <t>2013-10-12</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.007843961363015201</v>
+        <v>0.002348821150739861</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -11101,28 +12025,28 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2014-01-11</t>
+          <t>2013-10-19</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O71" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.007059565226713681</v>
+        <v>0.009395284602959443</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -11251,28 +12175,28 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2014-01-18</t>
+          <t>2013-10-26</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -11401,28 +12325,28 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2014-01-25</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O73" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P73" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -11551,28 +12475,28 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2014-02-01</t>
+          <t>2013-11-09</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.005490772954110641</v>
+        <v>0.0117441057536993</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -11701,12 +12625,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2014-02-08</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11722,7 +12646,7 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007059565226713681</v>
+        <v>0.007046463452219581</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -11851,28 +12775,28 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2014-02-15</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005490772954110641</v>
+        <v>0.006263523068639628</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -12001,28 +12925,28 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2014-02-22</t>
+          <t>2013-11-30</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P77" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.01017822498653939</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -12151,28 +13075,28 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2013-12-07</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.003921980681507601</v>
+        <v>0.003131761534319814</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -12301,28 +13225,28 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2014-03-08</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.008612344219379489</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -12451,28 +13375,28 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2014-03-15</t>
+          <t>2013-12-21</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.005480582685059674</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -12601,28 +13525,28 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2014-03-22</t>
+          <t>2013-12-28</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>0.003137584545206081</v>
+        <v>0.003914701917899767</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -12751,28 +13675,28 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2014-03-29</t>
+          <t>2014-01-04</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.007843961363015201</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -12901,28 +13825,28 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
+          <t>2014-01-11</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O83" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P83" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01019714977191976</v>
+        <v>0.007059565226713681</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -13051,12 +13975,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2014-04-12</t>
+          <t>2014-01-18</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13201,28 +14125,28 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2014-04-19</t>
+          <t>2014-01-25</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O85" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P85" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -13351,12 +14275,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2014-04-26</t>
+          <t>2014-02-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13501,28 +14425,28 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2014-05-03</t>
+          <t>2014-02-08</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O87" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P87" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.0117659420445228</v>
+        <v>0.007059565226713681</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -13651,28 +14575,28 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2014-05-10</t>
+          <t>2014-02-15</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.005490772954110641</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -13801,28 +14725,28 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2014-05-17</t>
+          <t>2014-02-22</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.005490772954110641</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -13951,28 +14875,28 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2014-05-24</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.003921980681507601</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -14101,28 +15025,28 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2014-05-31</t>
+          <t>2014-03-08</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.007843961363015201</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -14251,28 +15175,28 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2014-06-07</t>
+          <t>2014-03-15</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -14401,28 +15325,28 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2014-06-14</t>
+          <t>2014-03-22</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.003921980681507601</v>
+        <v>0.003137584545206081</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -14551,28 +15475,28 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2014-06-21</t>
+          <t>2014-03-29</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O94" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P94" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.007059565226713681</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -14701,28 +15625,28 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2014-06-28</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P95" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.01019714977191976</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -14851,28 +15775,28 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2014-07-05</t>
+          <t>2014-04-12</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.006275169090412163</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -15001,28 +15925,28 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2014-07-12</t>
+          <t>2014-04-19</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O97" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P97" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -15151,28 +16075,28 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2014-07-19</t>
+          <t>2014-04-26</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O98" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P98" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.01019714977191976</v>
+        <v>0.005490772954110641</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -15301,28 +16225,28 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2014-05-03</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O99" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P99" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.009412753635618243</v>
+        <v>0.0117659420445228</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -15451,28 +16375,28 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-05-10</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O100" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P100" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.009412753635618243</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -15601,12 +16525,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-05-17</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -15751,28 +16675,28 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2014-08-16</t>
+          <t>2014-05-24</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.003137584545206081</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -15901,28 +16825,28 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2014-08-23</t>
+          <t>2014-05-31</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.007843961363015201</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -16051,12 +16975,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2014-06-07</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -16201,12 +17125,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2014-09-06</t>
+          <t>2014-06-14</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -16351,28 +17275,28 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2014-09-13</t>
+          <t>2014-06-21</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.007059565226713681</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -16501,28 +17425,28 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2014-09-20</t>
+          <t>2014-06-28</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P107" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -16651,28 +17575,28 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2014-09-27</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O108" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P108" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.002353188408904561</v>
+        <v>0.006275169090412163</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -16801,28 +17725,28 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
+          <t>2014-07-12</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0.003137584545206081</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -16951,28 +17875,28 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2014-10-11</t>
+          <t>2014-07-19</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O110" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P110" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.007843961363015201</v>
+        <v>0.01019714977191976</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -17101,12 +18025,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2014-10-18</t>
+          <t>2014-07-26</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N111" t="n">
@@ -17251,28 +18175,28 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2014-10-25</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O112" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P112" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.004706376817809122</v>
+        <v>0.009412753635618243</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -17401,28 +18325,28 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>0.003137584545206081</v>
+        <v>0.005490772954110641</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -17551,28 +18475,28 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2014-11-08</t>
+          <t>2014-08-16</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.003921980681507601</v>
+        <v>0.003137584545206081</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -17701,28 +18625,28 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2014-11-15</t>
+          <t>2014-08-23</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O115" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P115" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.003921980681507601</v>
+        <v>0.008628357499316723</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -17851,28 +18775,28 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2014-11-22</t>
+          <t>2014-08-30</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O116" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P116" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.003137584545206081</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -18001,28 +18925,28 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2014-11-29</t>
+          <t>2014-09-06</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O117" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.009412753635618243</v>
+        <v>0.003921980681507601</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -18151,28 +19075,28 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2014-12-06</t>
+          <t>2014-09-13</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P118" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.007843961363015201</v>
+        <v>0.004706376817809122</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -18301,28 +19225,28 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2014-12-13</t>
+          <t>2014-09-20</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P119" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0.008628357499316723</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -18451,28 +19375,28 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2014-12-20</t>
+          <t>2014-09-27</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P120" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0.003921980681507601</v>
+        <v>0.002353188408904561</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -18601,12 +19525,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2014-12-27</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -18688,6 +19612,1806 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2014-10-11</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>10</v>
+      </c>
+      <c r="O122" t="n">
+        <v>10</v>
+      </c>
+      <c r="P122" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.007843961363015201</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2014-10-18</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>12</v>
+      </c>
+      <c r="O123" t="n">
+        <v>12</v>
+      </c>
+      <c r="P123" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.009412753635618243</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2014-10-25</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>6</v>
+      </c>
+      <c r="O124" t="n">
+        <v>6</v>
+      </c>
+      <c r="P124" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.004706376817809122</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>4</v>
+      </c>
+      <c r="O125" t="n">
+        <v>4</v>
+      </c>
+      <c r="P125" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.003137584545206081</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2014-11-08</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>5</v>
+      </c>
+      <c r="O126" t="n">
+        <v>5</v>
+      </c>
+      <c r="P126" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.003921980681507601</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2014-11-15</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>5</v>
+      </c>
+      <c r="O127" t="n">
+        <v>5</v>
+      </c>
+      <c r="P127" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.003921980681507601</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2014-11-22</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>4</v>
+      </c>
+      <c r="O128" t="n">
+        <v>4</v>
+      </c>
+      <c r="P128" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.003137584545206081</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2014-11-29</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>12</v>
+      </c>
+      <c r="O129" t="n">
+        <v>12</v>
+      </c>
+      <c r="P129" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.009412753635618243</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2014-12-06</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>10</v>
+      </c>
+      <c r="O130" t="n">
+        <v>10</v>
+      </c>
+      <c r="P130" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.007843961363015201</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2014-12-13</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>11</v>
+      </c>
+      <c r="O131" t="n">
+        <v>11</v>
+      </c>
+      <c r="P131" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.008628357499316723</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2014-12-20</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>5</v>
+      </c>
+      <c r="O132" t="n">
+        <v>5</v>
+      </c>
+      <c r="P132" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.003921980681507601</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2014-12-27</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>4</v>
+      </c>
+      <c r="O133" t="n">
+        <v>4</v>
+      </c>
+      <c r="P133" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.003137584545206081</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_28eb4a06a1114de3c3e948fa6b67</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18738,7 +21462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2012-09-15</t>
+          <t>2010-01-01</t>
         </is>
       </c>
     </row>
@@ -18819,7 +21543,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -18839,7 +21563,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -18849,7 +21573,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
